--- a/Tanvi_ExcelDashboard/Tanvi_ExcelDashboard.xlsx
+++ b/Tanvi_ExcelDashboard/Tanvi_ExcelDashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_alldata\practice\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_alldata\Excel\Tanvi_ExcelDashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35894C4-6699-4759-A539-A9449F86E84D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469A344E-EC7F-4589-AB46-3D5872B38017}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{5E3327AD-7332-4BF1-A17F-358847F0E2A9}"/>
   </bookViews>
@@ -2227,8 +2227,52 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2248,69 +2292,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -17204,6 +17190,129 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EAC42E7-0B22-4D66-8434-C549BBCE567D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="20">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="10" showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="16" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="13" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B3BEA81F-0BB8-4C19-910E-1923B9D9AD5D}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="G3:I7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
@@ -17677,7 +17786,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{121064E0-E411-4BFD-B8A2-393CF88EE6AC}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="20">
@@ -17766,129 +17875,6 @@
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5EAC42E7-0B22-4D66-8434-C549BBCE567D}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="20">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="10" showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Sales" fld="16" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="13" count="1" selected="0">
             <x v="0"/>
           </reference>
         </references>
@@ -18353,12 +18339,12 @@
       <c r="V1" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="W1" s="34" t="s">
+      <c r="W1" s="24" t="s">
         <v>582</v>
       </c>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="38"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="22"/>
       <c r="AA1" s="11" t="s">
         <v>596</v>
       </c>
@@ -18368,10 +18354,10 @@
       <c r="AC1" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="AD1" s="32" t="s">
+      <c r="AD1" s="26" t="s">
         <v>599</v>
       </c>
-      <c r="AE1" s="33"/>
+      <c r="AE1" s="27"/>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
@@ -18455,7 +18441,7 @@
       <c r="Z2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AA2" s="39">
+      <c r="AA2" s="23">
         <f>SUM(Q2:Q300)</f>
         <v>76821.329200000007</v>
       </c>
@@ -18467,8 +18453,8 @@
         <f>SUM(T2:T300)</f>
         <v>-509.85949999999991</v>
       </c>
-      <c r="AD2" s="33"/>
-      <c r="AE2" s="33"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
@@ -18541,24 +18527,24 @@
         <v>Medium Sales</v>
       </c>
       <c r="W3" s="6">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="X3" s="6" t="str">
         <f>VLOOKUP(W3,A2:T300,8,FALSE)</f>
-        <v>Zuschuss Donatelli</v>
-      </c>
-      <c r="Y3" s="37">
+        <v>Claire Gute</v>
+      </c>
+      <c r="Y3" s="21">
         <f>VLOOKUP(W3,A2:T300,5,FALSE)</f>
-        <v>40787</v>
-      </c>
-      <c r="Z3" s="37" t="str">
+        <v>41590</v>
+      </c>
+      <c r="Z3" s="21" t="str">
         <f>VLOOKUP(W3,A2:T300,7,FALSE)</f>
         <v>Second Class</v>
       </c>
-      <c r="AD3" s="28" t="s">
+      <c r="AD3" s="20" t="s">
         <v>604</v>
       </c>
-      <c r="AE3" s="28" t="s">
+      <c r="AE3" s="20" t="s">
         <v>605</v>
       </c>
     </row>
@@ -18632,10 +18618,10 @@
         <f t="shared" si="2"/>
         <v>Low Sales</v>
       </c>
-      <c r="AD4" s="27" t="s">
+      <c r="AD4" s="19" t="s">
         <v>600</v>
       </c>
-      <c r="AE4" s="26" t="s">
+      <c r="AE4" s="32" t="s">
         <v>601</v>
       </c>
     </row>
@@ -18709,7 +18695,7 @@
         <f t="shared" si="2"/>
         <v>Medium Sales</v>
       </c>
-      <c r="AE5" s="26"/>
+      <c r="AE5" s="32"/>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
@@ -18781,10 +18767,10 @@
         <f t="shared" si="2"/>
         <v>Low Sales</v>
       </c>
-      <c r="W6" s="34" t="s">
+      <c r="W6" s="24" t="s">
         <v>585</v>
       </c>
-      <c r="X6" s="35"/>
+      <c r="X6" s="25"/>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
@@ -18940,7 +18926,7 @@
         <f>INDEX(K:K,MATCH(W8,H:H,0))</f>
         <v>Los Angeles</v>
       </c>
-      <c r="AD8" s="17" t="s">
+      <c r="AD8" s="28" t="s">
         <v>602</v>
       </c>
       <c r="AE8" s="29"/>
@@ -19088,10 +19074,10 @@
         <f t="shared" si="2"/>
         <v>Low Sales</v>
       </c>
-      <c r="AD10" s="24" t="s">
+      <c r="AD10" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="AE10" s="25"/>
+      <c r="AE10" s="18"/>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
@@ -39707,32 +39693,32 @@
   <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="D1" s="21" t="s">
+      <c r="B1" s="34"/>
+      <c r="D1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="22"/>
-      <c r="G1" s="21" t="s">
+      <c r="E1" s="38"/>
+      <c r="G1" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="22"/>
-      <c r="J1" s="21" t="s">
+      <c r="H1" s="38"/>
+      <c r="J1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="22"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -40098,19 +40084,19 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="39" t="s">
         <v>592</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="39"/>
+      <c r="D2" s="39" t="s">
         <v>594</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="G2" s="23" t="s">
+      <c r="E2" s="39"/>
+      <c r="G2" s="39" t="s">
         <v>595</v>
       </c>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
